--- a/XLibur.Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -679,7 +679,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="6">
+  <x:dataValidations count="7">
     <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:A1">
       <x:formula1>1</x:formula1>
       <x:formula2>5</x:formula2>
@@ -690,6 +690,10 @@
     </x:dataValidation>
     <x:dataValidation type="date" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
       <x:formula1>36526</x:formula1>
+      <x:formula2/>
+    </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A5:A5">
+      <x:formula1>$C$1:$C$2</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
@@ -717,18 +721,6 @@
     <x:firstFooter/>
   </x:headerFooter>
   <x:tableParts count="0"/>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="">
-          <x14:formula1>
-            <xm:f>'Data Validation'!$C$1:$C$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>A5:A5</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </x:ext>
-  </x:extLst>
 </x:worksheet>
 </file>
 

--- a/XLibur.Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -505,7 +505,7 @@
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
-      <x:formula1>=YesNo</x:formula1>
+      <x:formula1>YesNo</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B1:B2">
@@ -697,7 +697,7 @@
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
-      <x:formula1>=YesNo</x:formula1>
+      <x:formula1>YesNo</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B1:B2">
@@ -899,7 +899,7 @@
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
-      <x:formula1>=YesNo</x:formula1>
+      <x:formula1>YesNo</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B1:B2">

--- a/XLibur.Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -470,66 +470,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="7">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:A1">
+    <x:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1">
       <x:formula1>1</x:formula1>
       <x:formula2>5</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." promptTitle="" prompt="" sqref="A2:A3">
+    <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." sqref="A2:A3">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="date" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
+    </x:dataValidation>
+    <x:dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
       <x:formula1>36526</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A5:A5">
+    </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A5">
       <x:formula1>$C$1:$C$2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
+    </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6:A6">
       <x:formula1>YesNo</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B1:B2">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B2">
       <x:formula1>1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B3:B4">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -619,116 +603,83 @@
     </x:row>
   </x:sheetData>
   <x:dataValidations count="8">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:B1 A2:A2 C4:D4 F4:F5 C5:C7 D7:D7">
+    <x:dataValidation type="decimal" operator="equal" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 A2:A2 C4:D4 F4:F5 C5:C7 D7:D7">
       <x:formula1>1.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A11:A14 C11:C12 E11:E14 B13:B14 D13:D14">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="notEqual" showInputMessage="1" showErrorMessage="1" sqref="A11:A14 C11:C12 E11:E14 B13:B14 D13:D14">
       <x:formula1>2.2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B12">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B12">
       <x:formula1>3.3</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D5:D6">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D6">
       <x:formula1>4.4</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C13:C14">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13:C14">
       <x:formula1>5.5</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D11:D12">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D12">
       <x:formula1>6.6</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G4:G5">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G5">
       <x:formula1>7.7</x:formula1>
       <x:formula2>8.8</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H1:H12">
+    <x:dataValidation type="decimal" operator="notBetween" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H12">
       <x:formula1>9.9</x:formula1>
       <x:formula2>10.1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="7">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:A1">
+    <x:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1">
       <x:formula1>1</x:formula1>
       <x:formula2>5</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." promptTitle="" prompt="" sqref="A2:A3">
+    <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." sqref="A2:A3">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="date" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
+    </x:dataValidation>
+    <x:dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
       <x:formula1>36526</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A5:A5">
+    </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A5">
       <x:formula1>$C$1:$C$2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
+    </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6:A6">
       <x:formula1>YesNo</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B1:B2">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B2">
       <x:formula1>1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B3:B4">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -818,108 +769,79 @@
     </x:row>
   </x:sheetData>
   <x:dataValidations count="8">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:B1 A2:A2 C4:D4 F4:F5 C5:C7 D7:D7">
+    <x:dataValidation type="decimal" operator="equal" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 A2:A2 C4:D4 F4:F5 C5:C7 D7:D7">
       <x:formula1>1.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A11:A14 C11:C12 E11:E14 B13:B14 D13:D14">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="notEqual" showInputMessage="1" showErrorMessage="1" sqref="A11:A14 C11:C12 E11:E14 B13:B14 D13:D14">
       <x:formula1>2.2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B12">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B12">
       <x:formula1>3.3</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D5:D6">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D6">
       <x:formula1>4.4</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C13:C14">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13:C14">
       <x:formula1>5.5</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D11:D12">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D12">
       <x:formula1>6.6</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G4:G5">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G5">
       <x:formula1>7.7</x:formula1>
       <x:formula2>8.8</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H1:H12">
+    <x:dataValidation type="decimal" operator="notBetween" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H12">
       <x:formula1>9.9</x:formula1>
       <x:formula2>10.1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="6">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:A1">
+    <x:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1">
       <x:formula1>1</x:formula1>
       <x:formula2>5</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." promptTitle="" prompt="" sqref="A2:A3">
+    <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." sqref="A2:A3">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="date" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
+    </x:dataValidation>
+    <x:dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
       <x:formula1>36526</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
+    </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6:A6">
       <x:formula1>YesNo</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B1:B2">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B2">
       <x:formula1>1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B3:B4">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Data Validation'!$C$1:$C$2</xm:f>
           </x14:formula1>
@@ -933,9 +855,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1025,43 +944,33 @@
     </x:row>
   </x:sheetData>
   <x:dataValidations count="8">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:B1 A2:A2 C4:D4 F4:F5 C5:C7 D7:D7">
+    <x:dataValidation type="decimal" operator="equal" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 A2:A2 C4:D4 F4:F5 C5:C7 D7:D7">
       <x:formula1>1.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A11:A14 C11:C12 E11:E14 B13:B14 D13:D14">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="notEqual" showInputMessage="1" showErrorMessage="1" sqref="A11:A14 C11:C12 E11:E14 B13:B14 D13:D14">
       <x:formula1>2.2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B12">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B12">
       <x:formula1>3.3</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D5:D6">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D6">
       <x:formula1>4.4</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C13:C14">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13:C14">
       <x:formula1>5.5</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D11:D12">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D12">
       <x:formula1>6.6</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G4:G5">
+    </x:dataValidation>
+    <x:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G5">
       <x:formula1>7.7</x:formula1>
       <x:formula2>8.8</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H1:H12">
+    <x:dataValidation type="decimal" operator="notBetween" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H12">
       <x:formula1>9.9</x:formula1>
       <x:formula2>10.1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>